--- a/data/trans_dic/P33B_R3-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P33B_R3-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,18; 8,32</t>
+          <t>2,54; 6,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,27; 12,36</t>
+          <t>7,12; 11,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,73; 9,27</t>
+          <t>5,35; 8,69</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,73%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,59; 14,43</t>
+          <t>7,66; 13,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,37; 17,51</t>
+          <t>12,2; 17,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,87; 15,33</t>
+          <t>10,72; 15,02</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,89%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,17; 19,73</t>
+          <t>12,5; 20,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,64; 24,67</t>
+          <t>17,98; 25,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,25; 21,34</t>
+          <t>16,46; 21,48</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>19,57%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,38; 24,91</t>
+          <t>12,83; 23,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,56; 22,11</t>
+          <t>18,07; 25,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,29; 20,86</t>
+          <t>16,53; 22,93</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,56%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,84; 12,36</t>
+          <t>5,41; 11,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,52; 14,19</t>
+          <t>8,59; 14,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,07; 12,13</t>
+          <t>7,69; 11,52</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,07%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,18; 20,97</t>
+          <t>13,1; 20,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21,57; 29,8</t>
+          <t>21,97; 30,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18,39; 23,79</t>
+          <t>18,4; 23,84</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>21,82%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14,82; 21,95</t>
+          <t>15,39; 21,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,46; 25,64</t>
+          <t>22,42; 28,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12,25; 22,13</t>
+          <t>19,72; 24,04</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>26,12%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,45; 22,9</t>
+          <t>18,26; 23,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>28,97; 34,8</t>
+          <t>28,22; 33,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,99; 27,71</t>
+          <t>24,07; 28,29</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>18,82%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11,43; 16,15</t>
+          <t>14,23; 16,82</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16,55; 21,85</t>
+          <t>20,84; 23,14</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15,09; 18,71</t>
+          <t>18,03; 19,66</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15624</t>
+          <t>14126</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27813</t>
+          <t>29182</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43438</t>
+          <t>43308</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9900; 25912</t>
+          <t>8105; 21898</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>21044; 35788</t>
+          <t>22514; 37540</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34441; 55749</t>
+          <t>33959; 55188</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>55201</t>
+          <t>56263</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>76483</t>
+          <t>80869</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>131684</t>
+          <t>137132</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39356; 74794</t>
+          <t>40671; 74053</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>63684; 90152</t>
+          <t>66662; 96833</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>112313; 158451</t>
+          <t>115498; 161747</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>49919</t>
+          <t>50829</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>73136</t>
+          <t>75969</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>123054</t>
+          <t>126798</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>38358; 62176</t>
+          <t>39379; 64113</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>61579; 86114</t>
+          <t>64085; 89116</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>107942; 141752</t>
+          <t>110490; 144227</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>56845</t>
+          <t>64861</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>80859</t>
+          <t>90768</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>137703</t>
+          <t>155630</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41822; 77865</t>
+          <t>47891; 87538</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>50242; 105200</t>
+          <t>76258; 108245</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>96862; 164418</t>
+          <t>131462; 182303</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15352</t>
+          <t>16308</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>22894</t>
+          <t>25051</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38246</t>
+          <t>41359</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10440; 22099</t>
+          <t>11121; 23409</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>17748; 29545</t>
+          <t>19480; 32009</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31234; 46944</t>
+          <t>33253; 49821</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>44954</t>
+          <t>44494</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>65323</t>
+          <t>68142</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>110277</t>
+          <t>112636</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>35551; 56534</t>
+          <t>35455; 55501</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>55443; 76604</t>
+          <t>57944; 79426</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>96838; 125320</t>
+          <t>98317; 127395</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>112230</t>
+          <t>130608</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>159693</t>
+          <t>194710</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>271923</t>
+          <t>325318</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>92390; 136813</t>
+          <t>110582; 155889</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>80343; 217739</t>
+          <t>173130; 217353</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>180345; 325840</t>
+          <t>293976; 358319</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>150206</t>
+          <t>167946</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>228297</t>
+          <t>257409</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>378502</t>
+          <t>425355</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>69175; 212722</t>
+          <t>145765; 189021</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>207218; 248924</t>
+          <t>234389; 277672</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>229979; 455639</t>
+          <t>392089; 460753</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>500330</t>
+          <t>545433</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>734497</t>
+          <t>822101</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1234827</t>
+          <t>1367535</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>395284; 558367</t>
+          <t>502273; 593798</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>605619; 799633</t>
+          <t>778040; 864171</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1074122; 1331942</t>
+          <t>1309728; 1428418</t>
         </is>
       </c>
     </row>
